--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89334</v>
+        <v>89336</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93076</v>
+        <v>93081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93425</v>
+        <v>93430</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89336</v>
+        <v>89338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93081</v>
+        <v>93083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91585</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91585</v>
+        <v>91587</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89338</v>
+        <v>89340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89340</v>
+        <v>89342</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89342</v>
+        <v>89343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93436</v>
+        <v>93437</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89343</v>
+        <v>89349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93437</v>
+        <v>93443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89349</v>
+        <v>89353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93443</v>
+        <v>93447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89353</v>
+        <v>89355</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89355</v>
+        <v>89368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93449</v>
+        <v>93462</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89368</v>
+        <v>89370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93462</v>
+        <v>93463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89370</v>
+        <v>89373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93463</v>
+        <v>93466</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89373</v>
+        <v>89383</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93466</v>
+        <v>93476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 38361-2025 artfynd.xlsx
+++ b/artfynd/A 38361-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136721935</v>
       </c>
       <c r="B2" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136721942</v>
       </c>
       <c r="B3" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136721941</v>
       </c>
       <c r="B4" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>136721926</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>136721928</v>
       </c>
       <c r="B6" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>136721929</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136721930</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>136721932</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>136721937</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>136721938</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>136721940</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>136721943</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136721948</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>136721950</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>136721951</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>136721952</v>
       </c>
       <c r="B17" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136721953</v>
       </c>
       <c r="B18" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>136721954</v>
       </c>
       <c r="B19" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>136721956</v>
       </c>
       <c r="B20" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136721927</v>
       </c>
       <c r="B21" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>136721931</v>
       </c>
       <c r="B22" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>136721933</v>
       </c>
       <c r="B23" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>136721934</v>
       </c>
       <c r="B24" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>136721944</v>
       </c>
       <c r="B25" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>136721945</v>
       </c>
       <c r="B26" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>136721955</v>
       </c>
       <c r="B27" t="n">
-        <v>89383</v>
+        <v>89384</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>136721939</v>
       </c>
       <c r="B28" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>136721936</v>
       </c>
       <c r="B29" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>136721946</v>
       </c>
       <c r="B30" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>136721947</v>
       </c>
       <c r="B31" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
         <v>136721949</v>
       </c>
       <c r="B32" t="n">
-        <v>93476</v>
+        <v>93477</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
